--- a/Data/FlightPlan/FPL_27OCT26.xlsx
+++ b/Data/FlightPlan/FPL_27OCT26.xlsx
@@ -278,474 +278,480 @@
     <t>12:25</t>
   </si>
   <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
     <t>DAD</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>TNN</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
     <t>14:25</t>
   </si>
   <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
     <t>15:45</t>
   </si>
   <si>
-    <t>16:15</t>
-  </si>
-  <si>
     <t>18:10</t>
   </si>
   <si>
     <t>20:20</t>
   </si>
   <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>TNN</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
     <t>VN-A633</t>
   </si>
   <si>
@@ -1163,7 +1169,7 @@
     <t>Total Record(s): 336</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 26, 2026 21:52</t>
+    <t xml:space="preserve">Generated on  Oct 26, 2026 23:42</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2781,7 +2787,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>642</v>
+        <v>152</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
@@ -2797,13 +2803,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H42" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I42" s="7">
         <v>89</v>
       </c>
-      <c t="s" r="I42" s="7">
-        <v>90</v>
-      </c>
       <c t="s" r="J42" s="7">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2814,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>643</v>
+        <v>971</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
@@ -2827,16 +2833,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2844,10 +2850,10 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c t="s" r="A44" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B44" s="7">
-        <v>154</v>
+        <v>972</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
@@ -2860,65 +2866,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I44" s="7">
+        <v>92</v>
+      </c>
+      <c t="s" r="J44" s="7">
         <v>93</v>
-      </c>
-      <c t="s" r="J44" s="7">
-        <v>94</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c t="s" r="A45" s="6">
-        <v>24</v>
-      </c>
-      <c r="B45" s="7">
-        <v>938</v>
-      </c>
-      <c t="s" r="C45" s="7">
-        <v>14</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c t="s" r="E45" s="7">
-        <v>85</v>
-      </c>
-      <c r="F45" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G45" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H45" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I45" s="7">
-        <v>95</v>
-      </c>
-      <c t="s" r="J45" s="7">
-        <v>96</v>
-      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
+      <c t="s" r="A46" s="6">
+        <v>13</v>
+      </c>
+      <c r="B46" s="7">
+        <v>933</v>
+      </c>
+      <c t="s" r="C46" s="7">
+        <v>14</v>
+      </c>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
+      <c t="s" r="E46" s="7">
+        <v>94</v>
+      </c>
+      <c r="F46" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G46" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H46" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I46" s="7">
+        <v>95</v>
+      </c>
+      <c t="s" r="J46" s="7">
+        <v>96</v>
+      </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
@@ -2928,29 +2934,29 @@
         <v>13</v>
       </c>
       <c r="B47" s="7">
-        <v>933</v>
+        <v>131</v>
       </c>
       <c t="s" r="C47" s="7">
         <v>14</v>
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2961,29 +2967,29 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>131</v>
+        <v>276</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
+        <v>94</v>
+      </c>
+      <c r="F48" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G48" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H48" s="8">
         <v>97</v>
       </c>
-      <c r="F48" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G48" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H48" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I48" s="7">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2994,29 +3000,29 @@
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
+        <v>94</v>
+      </c>
+      <c r="F49" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G49" s="8">
         <v>97</v>
       </c>
-      <c r="F49" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G49" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="H49" s="8">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3024,81 +3030,81 @@
     </row>
     <row r="50" ht="15" customHeight="1">
       <c t="s" r="A50" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B50" s="7">
-        <v>277</v>
+        <v>828</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H50" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="I50" s="7">
+        <v>100</v>
+      </c>
+      <c t="s" r="J50" s="7">
         <v>101</v>
-      </c>
-      <c t="s" r="H50" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I50" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>103</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
-      <c t="s" r="A51" s="6">
-        <v>24</v>
-      </c>
-      <c r="B51" s="7">
-        <v>828</v>
-      </c>
-      <c t="s" r="C51" s="7">
-        <v>14</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c t="s" r="E51" s="7">
-        <v>97</v>
-      </c>
-      <c r="F51" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G51" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H51" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I51" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J51" s="7">
-        <v>105</v>
-      </c>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
+      <c t="s" r="A52" s="6">
+        <v>13</v>
+      </c>
+      <c r="B52" s="7">
+        <v>495</v>
+      </c>
+      <c t="s" r="C52" s="7">
+        <v>14</v>
+      </c>
       <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
+      <c t="s" r="E52" s="7">
+        <v>102</v>
+      </c>
+      <c r="F52" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G52" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H52" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="I52" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J52" s="7">
+        <v>104</v>
+      </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
@@ -3108,29 +3114,29 @@
         <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c t="s" r="C53" s="7">
         <v>14</v>
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="H53" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H53" s="8">
-        <v>107</v>
-      </c>
       <c t="s" r="I53" s="7">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3141,29 +3147,29 @@
         <v>13</v>
       </c>
       <c r="B54" s="7">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c t="s" r="C54" s="7">
         <v>14</v>
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
+        <v>102</v>
+      </c>
+      <c r="F54" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G54" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H54" s="8">
         <v>106</v>
       </c>
-      <c r="F54" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G54" s="8">
+      <c t="s" r="I54" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J54" s="7">
         <v>107</v>
-      </c>
-      <c t="s" r="H54" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I54" s="7">
-        <v>109</v>
-      </c>
-      <c t="s" r="J54" s="7">
-        <v>64</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3174,29 +3180,29 @@
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c t="s" r="C55" s="7">
         <v>14</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
+        <v>102</v>
+      </c>
+      <c r="F55" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G55" s="8">
         <v>106</v>
       </c>
-      <c r="F55" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G55" s="8">
+      <c t="s" r="H55" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H55" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="I55" s="7">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3207,29 +3213,29 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c t="s" r="C56" s="7">
         <v>14</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
+        <v>102</v>
+      </c>
+      <c r="F56" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G56" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H56" s="8">
         <v>106</v>
       </c>
-      <c r="F56" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G56" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H56" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I56" s="7">
+        <v>110</v>
+      </c>
+      <c t="s" r="J56" s="7">
         <v>111</v>
-      </c>
-      <c t="s" r="J56" s="7">
-        <v>112</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3240,29 +3246,29 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c t="s" r="C57" s="7">
         <v>14</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
+        <v>102</v>
+      </c>
+      <c r="F57" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G57" s="8">
         <v>106</v>
       </c>
-      <c r="F57" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G57" s="8">
+      <c t="s" r="H57" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H57" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="I57" s="7">
+        <v>112</v>
+      </c>
+      <c t="s" r="J57" s="7">
         <v>113</v>
-      </c>
-      <c t="s" r="J57" s="7">
-        <v>114</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3273,29 +3279,29 @@
         <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c t="s" r="C58" s="7">
         <v>14</v>
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
+        <v>102</v>
+      </c>
+      <c r="F58" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G58" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H58" s="8">
         <v>106</v>
       </c>
-      <c r="F58" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G58" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H58" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I58" s="7">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3306,29 +3312,29 @@
         <v>13</v>
       </c>
       <c r="B59" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c t="s" r="C59" s="7">
         <v>14</v>
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
+        <v>102</v>
+      </c>
+      <c r="F59" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G59" s="8">
         <v>106</v>
       </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
+      <c t="s" r="H59" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H59" s="8">
-        <v>89</v>
-      </c>
       <c t="s" r="I59" s="7">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3339,78 +3345,78 @@
         <v>13</v>
       </c>
       <c r="B60" s="7">
-        <v>516</v>
+        <v>1513</v>
       </c>
       <c t="s" r="C60" s="7">
         <v>14</v>
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
+        <v>102</v>
+      </c>
+      <c r="F60" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G60" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H60" s="8">
         <v>106</v>
       </c>
-      <c r="F60" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G60" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H60" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I60" s="7">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c t="s" r="A61" s="6">
-        <v>13</v>
-      </c>
-      <c r="B61" s="7">
-        <v>1513</v>
-      </c>
-      <c t="s" r="C61" s="7">
-        <v>14</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c t="s" r="E61" s="7">
-        <v>106</v>
-      </c>
-      <c r="F61" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G61" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H61" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="I61" s="7">
-        <v>119</v>
-      </c>
-      <c t="s" r="J61" s="7">
-        <v>120</v>
-      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
+      <c t="s" r="A62" s="6">
+        <v>13</v>
+      </c>
+      <c r="B62" s="7">
+        <v>1942</v>
+      </c>
+      <c t="s" r="C62" s="7">
+        <v>14</v>
+      </c>
       <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
+      <c t="s" r="E62" s="7">
+        <v>118</v>
+      </c>
+      <c r="F62" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G62" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H62" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="I62" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J62" s="7">
+        <v>57</v>
+      </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
@@ -3420,29 +3426,29 @@
         <v>13</v>
       </c>
       <c r="B63" s="7">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c t="s" r="C63" s="7">
         <v>14</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="H63" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H63" s="8">
-        <v>122</v>
-      </c>
       <c t="s" r="I63" s="7">
+        <v>58</v>
+      </c>
+      <c t="s" r="J63" s="7">
         <v>96</v>
-      </c>
-      <c t="s" r="J63" s="7">
-        <v>57</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3453,29 +3459,29 @@
         <v>13</v>
       </c>
       <c r="B64" s="7">
-        <v>1943</v>
+        <v>187</v>
       </c>
       <c t="s" r="C64" s="7">
         <v>14</v>
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3483,81 +3489,81 @@
     </row>
     <row r="65" ht="15" customHeight="1">
       <c t="s" r="A65" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B65" s="7">
-        <v>187</v>
+        <v>862</v>
       </c>
       <c t="s" r="C65" s="7">
         <v>14</v>
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
+        <v>118</v>
+      </c>
+      <c r="F65" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G65" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H65" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I65" s="7">
         <v>121</v>
       </c>
-      <c r="F65" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G65" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H65" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I65" s="7">
-        <v>100</v>
-      </c>
       <c t="s" r="J65" s="7">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c t="s" r="A66" s="6">
-        <v>24</v>
-      </c>
-      <c r="B66" s="7">
-        <v>862</v>
-      </c>
-      <c t="s" r="C66" s="7">
-        <v>14</v>
-      </c>
+      <c r="A66" s="6"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c t="s" r="E66" s="7">
-        <v>121</v>
-      </c>
-      <c r="F66" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G66" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H66" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I66" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="J66" s="7">
-        <v>124</v>
-      </c>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
+      <c t="s" r="A67" s="6">
+        <v>13</v>
+      </c>
+      <c r="B67" s="7">
+        <v>405</v>
+      </c>
+      <c t="s" r="C67" s="7">
+        <v>14</v>
+      </c>
       <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
+      <c t="s" r="E67" s="7">
+        <v>123</v>
+      </c>
+      <c r="F67" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G67" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H67" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="I67" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="J67" s="7">
+        <v>120</v>
+      </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
@@ -3567,29 +3573,29 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>405</v>
+        <v>712</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>126</v>
       </c>
       <c t="s" r="I68" s="7">
+        <v>101</v>
+      </c>
+      <c t="s" r="J68" s="7">
         <v>127</v>
-      </c>
-      <c t="s" r="J68" s="7">
-        <v>96</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3600,14 +3606,14 @@
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3616,10 +3622,10 @@
         <v>126</v>
       </c>
       <c t="s" r="H69" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="I69" s="7">
         <v>128</v>
-      </c>
-      <c t="s" r="I69" s="7">
-        <v>105</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>129</v>
@@ -3633,29 +3639,29 @@
         <v>13</v>
       </c>
       <c r="B70" s="7">
-        <v>713</v>
+        <v>406</v>
       </c>
       <c t="s" r="C70" s="7">
         <v>14</v>
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3666,29 +3672,29 @@
         <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3699,29 +3705,29 @@
         <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="C72" s="7">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="H72" s="8">
         <v>20</v>
-      </c>
-      <c t="s" r="H72" s="8">
-        <v>126</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>132</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3732,29 +3738,29 @@
         <v>13</v>
       </c>
       <c r="B73" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c t="s" r="C73" s="7">
         <v>14</v>
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c t="s" r="I73" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="J73" s="7">
         <v>134</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>60</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3765,110 +3771,114 @@
         <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="H74" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H74" s="8">
-        <v>126</v>
-      </c>
       <c t="s" r="I74" s="7">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c t="s" r="A75" s="6">
-        <v>13</v>
-      </c>
-      <c r="B75" s="7">
-        <v>408</v>
-      </c>
-      <c t="s" r="C75" s="7">
-        <v>14</v>
-      </c>
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c t="s" r="E75" s="7">
-        <v>125</v>
-      </c>
-      <c r="F75" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G75" s="8">
-        <v>126</v>
-      </c>
-      <c t="s" r="H75" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I75" s="7">
-        <v>40</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>83</v>
-      </c>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
+      <c t="s" r="A76" s="6">
+        <v>13</v>
+      </c>
+      <c r="B76" s="7">
+        <v>869</v>
+      </c>
+      <c t="s" r="C76" s="7">
+        <v>14</v>
+      </c>
       <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
+      <c t="s" r="E76" s="7">
+        <v>135</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H76" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I76" s="7">
+        <v>27</v>
+      </c>
+      <c t="s" r="J76" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="K76" s="7">
+        <v>137</v>
+      </c>
       <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
+      <c t="s" r="M76" s="7">
+        <v>129</v>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c t="s" r="A77" s="6">
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>869</v>
+        <v>274</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3879,29 +3889,29 @@
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3912,29 +3922,29 @@
         <v>13</v>
       </c>
       <c r="B79" s="7">
-        <v>275</v>
+        <v>1803</v>
       </c>
       <c t="s" r="C79" s="7">
         <v>14</v>
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3945,78 +3955,78 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c t="s" r="H80" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I80" s="7">
         <v>141</v>
       </c>
-      <c t="s" r="I80" s="7">
-        <v>135</v>
-      </c>
       <c t="s" r="J80" s="7">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c t="s" r="A81" s="6">
-        <v>13</v>
-      </c>
-      <c r="B81" s="7">
-        <v>1804</v>
-      </c>
-      <c t="s" r="C81" s="7">
-        <v>14</v>
-      </c>
+      <c r="A81" s="6"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c t="s" r="E81" s="7">
-        <v>137</v>
-      </c>
-      <c r="F81" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G81" s="8">
-        <v>141</v>
-      </c>
-      <c t="s" r="H81" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I81" s="7">
-        <v>142</v>
-      </c>
-      <c t="s" r="J81" s="7">
-        <v>143</v>
-      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
+      <c t="s" r="A82" s="6">
+        <v>13</v>
+      </c>
+      <c r="B82" s="7">
+        <v>329</v>
+      </c>
+      <c t="s" r="C82" s="7">
+        <v>14</v>
+      </c>
       <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
+      <c t="s" r="E82" s="7">
+        <v>143</v>
+      </c>
+      <c r="F82" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G82" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H82" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I82" s="7">
+        <v>144</v>
+      </c>
+      <c t="s" r="J82" s="7">
+        <v>120</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -4026,29 +4036,29 @@
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>329</v>
+        <v>844</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c t="s" r="I83" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J83" s="7">
         <v>145</v>
-      </c>
-      <c t="s" r="J83" s="7">
-        <v>96</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4059,29 +4069,29 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H84" s="8">
         <v>29</v>
-      </c>
-      <c t="s" r="H84" s="8">
-        <v>56</v>
       </c>
       <c t="s" r="I84" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4092,29 +4102,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>845</v>
+        <v>446</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4125,82 +4135,82 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>446</v>
+        <v>145</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>148</v>
-      </c>
-      <c r="K86" s="7"/>
+        <v>149</v>
+      </c>
+      <c t="s" r="K86" s="7">
+        <v>40</v>
+      </c>
       <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
+      <c t="s" r="M86" s="7">
+        <v>117</v>
+      </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
-      <c t="s" r="A87" s="6">
-        <v>13</v>
-      </c>
-      <c r="B87" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="C87" s="7">
-        <v>14</v>
-      </c>
+      <c r="A87" s="6"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="7"/>
-      <c t="s" r="E87" s="7">
-        <v>144</v>
-      </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H87" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I87" s="7">
-        <v>149</v>
-      </c>
-      <c t="s" r="J87" s="7">
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" ht="14.25" customHeight="1">
+      <c t="s" r="A88" s="6">
+        <v>13</v>
+      </c>
+      <c r="B88" s="7">
+        <v>724</v>
+      </c>
+      <c t="s" r="C88" s="7">
+        <v>14</v>
+      </c>
+      <c r="D88" s="7"/>
+      <c t="s" r="E88" s="7">
         <v>150</v>
       </c>
-      <c t="s" r="K87" s="7">
-        <v>40</v>
-      </c>
-      <c r="L87" s="7"/>
-      <c t="s" r="M87" s="7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="88" ht="14.25" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
+      <c r="F88" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G88" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="H88" s="8">
+        <v>97</v>
+      </c>
+      <c t="s" r="I88" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J88" s="7">
+        <v>151</v>
+      </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
@@ -4210,29 +4220,29 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4243,69 +4253,73 @@
         <v>13</v>
       </c>
       <c r="B90" s="7">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c t="s" r="C90" s="7">
         <v>14</v>
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>153</v>
-      </c>
-      <c r="K90" s="7"/>
+        <v>133</v>
+      </c>
+      <c t="s" r="K90" s="7">
+        <v>68</v>
+      </c>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>133</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c t="s" r="K91" s="7">
-        <v>68</v>
+        <v>154</v>
       </c>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4313,86 +4327,82 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>728</v>
+        <v>522</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c t="s" r="A93" s="6">
-        <v>13</v>
-      </c>
-      <c r="B93" s="7">
-        <v>522</v>
-      </c>
-      <c t="s" r="C93" s="7">
-        <v>14</v>
-      </c>
+      <c r="A93" s="6"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
       <c r="D93" s="7"/>
-      <c t="s" r="E93" s="7">
-        <v>151</v>
-      </c>
-      <c r="F93" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G93" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H93" s="8">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
+    </row>
+    <row r="94" ht="14.25" customHeight="1">
+      <c t="s" r="A94" s="6">
+        <v>13</v>
+      </c>
+      <c r="B94" s="7">
+        <v>929</v>
+      </c>
+      <c t="s" r="C94" s="7">
+        <v>14</v>
+      </c>
+      <c r="D94" s="7"/>
+      <c t="s" r="E94" s="7">
+        <v>158</v>
+      </c>
+      <c r="F94" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G94" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="I93" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="J93" s="7">
-        <v>71</v>
-      </c>
-      <c t="s" r="K93" s="7">
-        <v>157</v>
-      </c>
-      <c r="L93" s="7"/>
-      <c t="s" r="M93" s="7">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" ht="14.25" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
+      <c t="s" r="H94" s="8">
+        <v>159</v>
+      </c>
+      <c t="s" r="I94" s="7">
+        <v>32</v>
+      </c>
+      <c t="s" r="J94" s="7">
+        <v>160</v>
+      </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
@@ -4402,7 +4412,7 @@
         <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
@@ -4415,16 +4425,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
+        <v>159</v>
+      </c>
+      <c t="s" r="H95" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H95" s="8">
-        <v>159</v>
-      </c>
       <c t="s" r="I95" s="7">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4435,7 +4445,7 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>928</v>
+        <v>783</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
@@ -4448,27 +4458,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>116</v>
-      </c>
-      <c r="K96" s="7"/>
+        <v>22</v>
+      </c>
+      <c t="s" r="K96" s="7">
+        <v>163</v>
+      </c>
       <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
+      <c t="s" r="M96" s="7">
+        <v>164</v>
+      </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c t="s" r="A97" s="6">
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>971</v>
+        <v>772</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
@@ -4481,27 +4495,31 @@
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
+        <v>161</v>
+      </c>
+      <c t="s" r="H97" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H97" s="8">
-        <v>161</v>
-      </c>
       <c t="s" r="I97" s="7">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>82</v>
-      </c>
-      <c r="K97" s="7"/>
+        <v>156</v>
+      </c>
+      <c t="s" r="K97" s="7">
+        <v>70</v>
+      </c>
       <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
+      <c t="s" r="M97" s="7">
+        <v>165</v>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c t="s" r="A98" s="6">
         <v>24</v>
       </c>
       <c r="B98" s="7">
-        <v>972</v>
+        <v>938</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
@@ -4514,16 +4532,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4556,7 +4574,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4565,13 +4583,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4589,13 +4607,13 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>20</v>
@@ -4622,7 +4640,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4634,10 +4652,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4655,7 +4673,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4667,10 +4685,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4688,7 +4706,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4700,10 +4718,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4721,7 +4739,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4733,10 +4751,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4769,7 +4787,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4781,10 +4799,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4802,7 +4820,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4814,10 +4832,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4835,7 +4853,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4844,13 +4862,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4868,13 +4886,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>20</v>
@@ -4883,7 +4901,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4901,7 +4919,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4910,13 +4928,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4934,19 +4952,19 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>155</v>
@@ -4982,7 +5000,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4991,13 +5009,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5015,13 +5033,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>17</v>
@@ -5030,7 +5048,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5048,7 +5066,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5060,7 +5078,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>64</v>
@@ -5081,7 +5099,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5093,7 +5111,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>58</v>
@@ -5114,7 +5132,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5126,10 +5144,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5147,7 +5165,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5162,7 +5180,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5180,7 +5198,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5189,13 +5207,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5213,22 +5231,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5246,7 +5264,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5255,13 +5273,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5279,22 +5297,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5327,7 +5345,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5336,13 +5354,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I125" s="7">
+        <v>104</v>
+      </c>
+      <c t="s" r="J125" s="7">
         <v>108</v>
-      </c>
-      <c t="s" r="J125" s="7">
-        <v>111</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5360,13 +5378,13 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>17</v>
@@ -5404,11 +5422,11 @@
         <v>5521</v>
       </c>
       <c t="s" r="C128" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5420,17 +5438,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="K128" s="7">
         <v>43</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5445,7 +5463,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5457,10 +5475,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5478,7 +5496,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5487,13 +5505,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5511,13 +5529,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
@@ -5526,7 +5544,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5544,7 +5562,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5553,13 +5571,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5577,19 +5595,19 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>157</v>
@@ -5610,7 +5628,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5622,10 +5640,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5658,7 +5676,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5670,10 +5688,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5691,7 +5709,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5703,10 +5721,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5724,7 +5742,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5736,10 +5754,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5757,7 +5775,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5772,7 +5790,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5790,7 +5808,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5799,13 +5817,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5823,22 +5841,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5856,7 +5874,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5865,13 +5883,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5889,22 +5907,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5937,7 +5955,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5946,13 +5964,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5970,22 +5988,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6003,7 +6021,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6012,13 +6030,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6036,22 +6054,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6069,7 +6087,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6078,13 +6096,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6102,22 +6120,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6135,7 +6153,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6147,7 +6165,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>42</v>
@@ -6183,7 +6201,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6192,7 +6210,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I153" s="7">
         <v>37</v>
@@ -6212,17 +6230,17 @@
         <v>6888</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>20</v>
@@ -6245,11 +6263,11 @@
         <v>6888</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6264,7 +6282,7 @@
         <v>226</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6315,7 +6333,7 @@
         <v>229</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
@@ -6346,7 +6364,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>31</v>
@@ -6427,10 +6445,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6457,7 +6475,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>233</v>
@@ -6487,13 +6505,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>39</v>
@@ -6643,7 +6661,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6687,7 +6705,7 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>152</v>
+        <v>642</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
@@ -6703,13 +6721,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6720,7 +6738,7 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>783</v>
+        <v>643</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
@@ -6733,16 +6751,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6753,7 +6771,7 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>772</v>
+        <v>154</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
@@ -6766,16 +6784,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6808,7 +6826,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6820,7 +6838,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>49</v>
@@ -6841,7 +6859,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6850,13 +6868,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6874,22 +6892,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6907,7 +6925,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6916,13 +6934,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6940,13 +6958,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>16</v>
@@ -6955,7 +6973,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6988,7 +7006,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7000,7 +7018,7 @@
         <v>66</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>77</v>
@@ -7021,7 +7039,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7033,7 +7051,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>37</v>
@@ -7054,7 +7072,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7063,13 +7081,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7087,19 +7105,19 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>157</v>
@@ -7120,7 +7138,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7129,13 +7147,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>42</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7153,22 +7171,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7201,7 +7219,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7210,13 +7228,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7234,22 +7252,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7267,22 +7285,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7300,22 +7318,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7333,7 +7351,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7342,13 +7360,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7366,22 +7384,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7414,22 +7432,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7447,7 +7465,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7456,13 +7474,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7480,22 +7498,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7513,7 +7531,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7522,13 +7540,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H197" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="I197" s="7">
         <v>89</v>
       </c>
-      <c t="s" r="I197" s="7">
-        <v>100</v>
-      </c>
       <c t="s" r="J197" s="7">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7561,7 +7579,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7570,13 +7588,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>239</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7594,22 +7612,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7627,7 +7645,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7639,10 +7657,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7660,7 +7678,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7672,10 +7690,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7693,7 +7711,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7702,13 +7720,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7726,22 +7744,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7759,7 +7777,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7768,10 +7786,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>155</v>
@@ -7807,7 +7825,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7816,13 +7834,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7840,22 +7858,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7873,7 +7891,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7882,13 +7900,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7906,22 +7924,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7939,22 +7957,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7987,7 +8005,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7999,10 +8017,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8020,7 +8038,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8032,10 +8050,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8053,7 +8071,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8062,13 +8080,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8086,22 +8104,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8119,7 +8137,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8128,7 +8146,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>36</v>
@@ -8152,13 +8170,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>17</v>
@@ -8185,7 +8203,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8197,10 +8215,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8218,7 +8236,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8230,7 +8248,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>224</v>
@@ -8266,7 +8284,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8278,10 +8296,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8299,7 +8317,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8308,7 +8326,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I223" s="7">
         <v>243</v>
@@ -8332,19 +8350,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>22</v>
@@ -8365,7 +8383,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8380,7 +8398,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8413,22 +8431,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8446,22 +8464,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>93</v>
+        <v>245</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8479,25 +8497,25 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>236</v>
       </c>
       <c t="s" r="K229" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
@@ -8531,7 +8549,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8540,13 +8558,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8564,19 +8582,19 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>87</v>
@@ -8597,7 +8615,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8609,7 +8627,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>22</v>
@@ -8630,7 +8648,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8645,7 +8663,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8678,19 +8696,19 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>65</v>
@@ -8711,22 +8729,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8744,22 +8762,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8792,7 +8810,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8804,10 +8822,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8825,7 +8843,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8837,7 +8855,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>64</v>
@@ -8858,7 +8876,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8891,7 +8909,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8903,7 +8921,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>78</v>
@@ -8924,7 +8942,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8933,13 +8951,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>233</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8957,29 +8975,29 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9009,7 +9027,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9018,13 +9036,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9042,22 +9060,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9075,22 +9093,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9108,13 +9126,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>17</v>
@@ -9123,7 +9141,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9141,7 +9159,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9150,20 +9168,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>154</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9193,7 +9211,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9202,13 +9220,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9226,22 +9244,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9259,7 +9277,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9268,13 +9286,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9292,13 +9310,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
@@ -9307,7 +9325,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9325,7 +9343,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9334,10 +9352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>153</v>
@@ -9358,19 +9376,19 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>60</v>
@@ -9391,7 +9409,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9424,7 +9442,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9436,7 +9454,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>26</v>
@@ -9472,7 +9490,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9481,13 +9499,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9505,19 +9523,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>88</v>
@@ -9538,7 +9556,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9547,13 +9565,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9571,22 +9589,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9615,17 +9633,17 @@
         <v>37</v>
       </c>
       <c t="s" r="C267" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>20</v>
@@ -9634,7 +9652,7 @@
         <v>233</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9667,7 +9685,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9676,13 +9694,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9700,22 +9718,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9733,7 +9751,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9742,13 +9760,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9766,22 +9784,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9799,7 +9817,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9847,7 +9865,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9856,13 +9874,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9880,13 +9898,13 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>20</v>
@@ -9895,7 +9913,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9913,7 +9931,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9922,7 +9940,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>87</v>
@@ -9946,22 +9964,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9979,7 +9997,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9988,10 +10006,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>23</v>
@@ -10012,19 +10030,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>38</v>
@@ -10045,7 +10063,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10054,13 +10072,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10078,13 +10096,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>20</v>
@@ -10093,7 +10111,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10126,13 +10144,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>20</v>
@@ -10159,7 +10177,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10174,7 +10192,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10192,7 +10210,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10207,7 +10225,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10225,7 +10243,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10237,10 +10255,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10273,7 +10291,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10282,13 +10300,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10306,13 +10324,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>20</v>
@@ -10321,7 +10339,7 @@
         <v>243</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10339,7 +10357,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10348,13 +10366,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10372,22 +10390,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10420,7 +10438,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10432,10 +10450,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10453,7 +10471,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10462,13 +10480,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10486,13 +10504,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>20</v>
@@ -10501,7 +10519,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10534,7 +10552,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10546,10 +10564,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10567,7 +10585,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10579,10 +10597,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10600,7 +10618,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10615,7 +10633,7 @@
         <v>233</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10633,7 +10651,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10645,7 +10663,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>39</v>
@@ -10666,7 +10684,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10678,10 +10696,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10714,7 +10732,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10723,13 +10741,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10747,22 +10765,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10780,7 +10798,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10789,10 +10807,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>160</v>
@@ -10813,13 +10831,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>17</v>
@@ -10846,7 +10864,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10855,13 +10873,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10879,22 +10897,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10927,7 +10945,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10936,13 +10954,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10960,13 +10978,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>56</v>
@@ -10975,7 +10993,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10993,7 +11011,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11002,7 +11020,7 @@
         <v>56</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>52</v>
@@ -11022,26 +11040,26 @@
         <v>5840</v>
       </c>
       <c t="s" r="C314" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>235</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11055,11 +11073,11 @@
         <v>5841</v>
       </c>
       <c t="s" r="C315" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11068,13 +11086,13 @@
         <v>235</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11107,7 +11125,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11119,10 +11137,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11140,7 +11158,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11155,7 +11173,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11173,7 +11191,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11182,10 +11200,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>67</v>
@@ -11206,19 +11224,19 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>21</v>
@@ -11239,7 +11257,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11248,7 +11266,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>234</v>
@@ -11287,7 +11305,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11299,7 +11317,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>243</v>
@@ -11320,7 +11338,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11329,13 +11347,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11353,22 +11371,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11401,7 +11419,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11410,13 +11428,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11434,22 +11452,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11467,7 +11485,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11482,7 +11500,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11500,7 +11518,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11512,7 +11530,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>52</v>
@@ -11533,7 +11551,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11548,7 +11566,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11566,7 +11584,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11578,10 +11596,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11614,7 +11632,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11626,10 +11644,10 @@
         <v>159</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11647,7 +11665,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11662,7 +11680,7 @@
         <v>243</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11680,7 +11698,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11689,13 +11707,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11713,13 +11731,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
@@ -11728,7 +11746,7 @@
         <v>236</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11761,7 +11779,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11776,7 +11794,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11794,7 +11812,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11803,13 +11821,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>75</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11827,22 +11845,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11860,7 +11878,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11872,10 +11890,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11893,7 +11911,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11902,13 +11920,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11926,19 +11944,19 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>43</v>
@@ -11974,7 +11992,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -11983,13 +12001,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12007,19 +12025,19 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>76</v>
@@ -12040,19 +12058,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>78</v>
@@ -12073,16 +12091,16 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>36</v>
@@ -12106,22 +12124,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12139,13 +12157,13 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>17</v>
@@ -12154,7 +12172,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12187,7 +12205,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12196,20 +12214,20 @@
         <v>41</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12224,16 +12242,16 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>229</v>
@@ -12257,19 +12275,19 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>60</v>
@@ -12290,22 +12308,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12338,7 +12356,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12350,10 +12368,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12371,7 +12389,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12380,10 +12398,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>229</v>
@@ -12404,19 +12422,19 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>79</v>
@@ -12437,7 +12455,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12446,13 +12464,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12470,22 +12488,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12503,7 +12521,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12515,10 +12533,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12551,7 +12569,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12560,10 +12578,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>32</v>
@@ -12584,22 +12602,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12617,7 +12635,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12626,10 +12644,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>88</v>
@@ -12650,22 +12668,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12683,7 +12701,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12692,10 +12710,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>40</v>
@@ -12716,22 +12734,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12764,22 +12782,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12797,7 +12815,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12809,10 +12827,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12830,7 +12848,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12839,13 +12857,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12863,19 +12881,19 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>234</v>
@@ -12896,7 +12914,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12905,10 +12923,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>70</v>
@@ -12929,22 +12947,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12973,29 +12991,29 @@
         <v>5228</v>
       </c>
       <c t="s" r="C379" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
@@ -13010,17 +13028,17 @@
         <v>5574</v>
       </c>
       <c t="s" r="C380" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F380" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>29</v>
@@ -13029,14 +13047,14 @@
         <v>69</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="K380" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13066,7 +13084,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
@@ -13075,7 +13093,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>64</v>
@@ -13095,26 +13113,26 @@
         <v>6874</v>
       </c>
       <c t="s" r="C383" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F383" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13128,26 +13146,26 @@
         <v>6875</v>
       </c>
       <c t="s" r="C384" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13180,7 +13198,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13195,7 +13213,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13213,7 +13231,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
@@ -13225,10 +13243,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13246,7 +13264,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13258,7 +13276,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>154</v>
@@ -13279,7 +13297,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13288,7 +13306,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>70</v>
@@ -13327,7 +13345,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
@@ -13339,10 +13357,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13360,7 +13378,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
@@ -13393,7 +13411,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13408,7 +13426,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13441,7 +13459,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13450,13 +13468,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13474,22 +13492,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13507,22 +13525,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13555,7 +13573,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13570,7 +13588,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13588,7 +13606,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13621,7 +13639,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13630,10 +13648,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>59</v>
@@ -13654,13 +13672,13 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>20</v>
@@ -13669,7 +13687,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13687,7 +13705,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13735,7 +13753,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -13747,7 +13765,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>64</v>
@@ -13768,7 +13786,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -13780,7 +13798,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>49</v>
@@ -13816,7 +13834,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13825,10 +13843,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>71</v>
@@ -13849,19 +13867,19 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>241</v>
@@ -13872,7 +13890,7 @@
     </row>
     <row r="410" ht="16.5" customHeight="1">
       <c t="s" r="A410" s="9">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
@@ -13892,7 +13910,7 @@
     <row r="411" ht="65.25" customHeight="1"/>
     <row r="412" ht="16.5" customHeight="1">
       <c t="s" r="A412" s="10">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B412" s="10"/>
       <c r="C412" s="10"/>
@@ -13905,7 +13923,7 @@
       <c r="J412" s="10"/>
       <c r="K412" s="10"/>
       <c t="s" r="L412" s="11">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M412" s="11"/>
       <c r="N412" s="11"/>

--- a/Data/FlightPlan/FPL_27OCT26.xlsx
+++ b/Data/FlightPlan/FPL_27OCT26.xlsx
@@ -107,12 +107,21 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:21</t>
+  </si>
+  <si>
     <t>08:40</t>
   </si>
   <si>
     <t>09:45</t>
   </si>
   <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
     <t>TXN</t>
   </si>
   <si>
@@ -296,9 +305,6 @@
     <t>VN-A526</t>
   </si>
   <si>
-    <t>09:30</t>
-  </si>
-  <si>
     <t>14:00</t>
   </si>
   <si>
@@ -374,6 +380,15 @@
     <t>07:50</t>
   </si>
   <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
     <t>02:40</t>
   </si>
   <si>
@@ -638,9 +653,6 @@
     <t>07:45</t>
   </si>
   <si>
-    <t>14:30</t>
-  </si>
-  <si>
     <t>15:10</t>
   </si>
   <si>
@@ -812,9 +824,6 @@
     <t>VN-A637</t>
   </si>
   <si>
-    <t>12:40</t>
-  </si>
-  <si>
     <t>VN-A639</t>
   </si>
   <si>
@@ -833,9 +842,6 @@
     <t>06:25</t>
   </si>
   <si>
-    <t>10:35</t>
-  </si>
-  <si>
     <t>12:55</t>
   </si>
   <si>
@@ -899,9 +905,6 @@
     <t>VN-A648</t>
   </si>
   <si>
-    <t>08:35</t>
-  </si>
-  <si>
     <t>09:05</t>
   </si>
   <si>
@@ -1169,7 +1172,7 @@
     <t>Total Record(s): 336</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 26, 2026 23:42</t>
+    <t xml:space="preserve">Generated on  Oct 27, 2026 03:38</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1880,7 +1883,9 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c t="s" r="M11" s="7">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c t="s" r="A12" s="6">
@@ -1906,14 +1911,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I12" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J12" s="7">
-        <v>33</v>
-      </c>
-      <c r="K12" s="7"/>
+        <v>34</v>
+      </c>
+      <c t="s" r="K12" s="7">
+        <v>35</v>
+      </c>
       <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+      <c t="s" r="M12" s="7">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c t="s" r="A13" s="6">
@@ -1936,13 +1945,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H13" s="8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -1966,16 +1975,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G14" s="8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c t="s" r="H14" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2005,10 +2014,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I15" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c t="s" r="J15" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -2035,13 +2044,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H16" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="I16" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c t="s" r="J16" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
@@ -2074,22 +2083,22 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G18" s="8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c t="s" r="H18" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2107,7 +2116,7 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
@@ -2116,13 +2125,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2140,22 +2149,22 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H20" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2173,7 +2182,7 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
@@ -2182,10 +2191,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c t="s" r="J21" s="7">
         <v>27</v>
@@ -2221,7 +2230,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2230,13 +2239,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="I23" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2254,22 +2263,22 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="H24" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2287,7 +2296,7 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
@@ -2299,10 +2308,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2320,7 +2329,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2332,10 +2341,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2368,22 +2377,22 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G28" s="8">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c t="s" r="H28" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2401,7 +2410,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2410,10 +2419,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H29" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c t="s" r="J29" s="7">
         <v>21</v>
@@ -2434,22 +2443,22 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G30" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="H30" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2467,7 +2476,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2479,10 +2488,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2515,7 +2524,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2524,13 +2533,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2548,22 +2557,22 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2581,7 +2590,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2590,13 +2599,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2614,22 +2623,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2647,7 +2656,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2656,13 +2665,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2680,22 +2689,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2728,7 +2737,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2737,13 +2746,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2761,22 +2770,22 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2794,7 +2803,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2806,10 +2815,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2827,7 +2836,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2836,13 +2845,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2860,22 +2869,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2908,7 +2917,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2920,10 +2929,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2941,7 +2950,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2953,10 +2962,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2974,7 +2983,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -2983,13 +2992,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3007,22 +3016,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3040,7 +3049,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3049,13 +3058,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3088,7 +3097,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3097,13 +3106,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3121,22 +3130,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3154,7 +3163,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3163,13 +3172,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3187,22 +3196,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3220,7 +3229,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3229,13 +3238,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3253,22 +3262,22 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3286,7 +3295,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3295,13 +3304,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3319,22 +3328,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3352,7 +3361,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3361,13 +3370,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3400,7 +3409,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3409,17 +3418,21 @@
         <v>20</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>57</v>
-      </c>
-      <c r="K62" s="7"/>
+        <v>60</v>
+      </c>
+      <c t="s" r="K62" s="7">
+        <v>123</v>
+      </c>
       <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
+      <c t="s" r="M62" s="7">
+        <v>78</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
@@ -3433,26 +3446,30 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>96</v>
-      </c>
-      <c r="K63" s="7"/>
+        <v>98</v>
+      </c>
+      <c t="s" r="K63" s="7">
+        <v>124</v>
+      </c>
       <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
+      <c t="s" r="M63" s="7">
+        <v>125</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c t="s" r="A64" s="6">
@@ -3466,7 +3483,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3478,10 +3495,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3499,7 +3516,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3511,10 +3528,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3547,7 +3564,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3556,13 +3573,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3580,22 +3597,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3613,22 +3630,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3646,19 +3663,19 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>19</v>
@@ -3679,7 +3696,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3688,13 +3705,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3712,22 +3729,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3745,7 +3762,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3754,13 +3771,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3778,22 +3795,22 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3826,13 +3843,13 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>17</v>
@@ -3841,14 +3858,14 @@
         <v>27</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="K76" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -3863,7 +3880,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3872,13 +3889,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3896,22 +3913,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3929,7 +3946,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3938,13 +3955,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3962,22 +3979,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4010,7 +4027,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4022,10 +4039,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4043,7 +4060,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4052,13 +4069,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4076,22 +4093,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4109,7 +4126,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4121,10 +4138,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4142,7 +4159,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4154,17 +4171,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c t="s" r="K86" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4194,22 +4211,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I88" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4227,22 +4244,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4260,29 +4277,29 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c t="s" r="K90" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4297,29 +4314,29 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c t="s" r="K91" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4334,29 +4351,29 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4386,7 +4403,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4395,13 +4412,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4419,22 +4436,22 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4452,7 +4469,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4461,20 +4478,20 @@
         <v>20</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>22</v>
       </c>
       <c t="s" r="K96" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4489,29 +4506,29 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4526,7 +4543,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4535,13 +4552,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4574,7 +4591,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4583,13 +4600,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4607,22 +4624,22 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4640,7 +4657,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4652,10 +4669,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4673,7 +4690,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4685,10 +4702,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4706,7 +4723,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4718,10 +4735,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4739,7 +4756,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4751,10 +4768,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4787,7 +4804,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4799,10 +4816,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4820,7 +4837,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4832,10 +4849,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4853,7 +4870,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4862,13 +4879,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4886,22 +4903,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4919,7 +4936,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4928,13 +4945,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4952,22 +4969,22 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5000,7 +5017,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5009,13 +5026,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5033,13 +5050,13 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>17</v>
@@ -5048,7 +5065,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5066,7 +5083,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5078,10 +5095,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5099,7 +5116,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5111,10 +5128,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5132,7 +5149,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5144,10 +5161,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5165,7 +5182,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5180,7 +5197,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5198,7 +5215,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5207,13 +5224,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5231,22 +5248,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5264,7 +5281,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5273,13 +5290,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5297,22 +5314,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5345,7 +5362,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5354,13 +5371,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5378,13 +5395,13 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>17</v>
@@ -5393,7 +5410,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5422,11 +5439,11 @@
         <v>5521</v>
       </c>
       <c t="s" r="C128" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5438,17 +5455,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5463,7 +5480,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5475,10 +5492,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5496,7 +5513,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5505,13 +5522,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5529,22 +5546,22 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5562,7 +5579,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5571,13 +5588,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5595,22 +5612,22 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5628,7 +5645,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5640,10 +5657,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5676,7 +5693,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5685,13 +5702,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5709,22 +5726,22 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5742,7 +5759,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5754,10 +5771,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5775,7 +5792,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5787,10 +5804,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5808,7 +5825,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5817,13 +5834,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5841,22 +5858,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5874,7 +5891,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5883,13 +5900,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5907,22 +5924,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5955,7 +5972,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5964,13 +5981,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5988,22 +6005,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6021,7 +6038,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6030,13 +6047,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6054,22 +6071,22 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6087,7 +6104,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6096,13 +6113,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6120,22 +6137,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6153,7 +6170,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6165,10 +6182,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6201,7 +6218,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6210,13 +6227,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6230,26 +6247,26 @@
         <v>6888</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6263,11 +6280,11 @@
         <v>6888</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6276,13 +6293,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6315,7 +6332,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6327,17 +6344,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6352,7 +6369,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6364,7 +6381,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>31</v>
@@ -6400,7 +6417,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6409,13 +6426,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6433,22 +6450,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6466,7 +6483,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6475,13 +6492,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6499,22 +6516,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6532,7 +6549,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6541,13 +6558,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6565,22 +6582,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6613,7 +6630,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6625,10 +6642,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6646,7 +6663,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6658,10 +6675,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6679,7 +6696,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6691,10 +6708,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6712,7 +6729,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6721,13 +6738,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6745,19 +6762,19 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>21</v>
@@ -6778,7 +6795,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6790,10 +6807,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6826,7 +6843,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6838,10 +6855,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6859,7 +6876,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6868,13 +6885,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6892,22 +6909,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6925,7 +6942,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6934,13 +6951,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6958,22 +6975,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7006,7 +7023,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7015,13 +7032,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7039,22 +7056,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7072,7 +7089,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7081,13 +7098,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7105,22 +7122,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7138,7 +7155,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7147,13 +7164,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7171,22 +7188,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7219,7 +7236,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7228,13 +7245,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7252,22 +7269,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7285,22 +7302,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7318,22 +7335,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7351,7 +7368,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7360,13 +7377,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7384,22 +7401,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7432,22 +7449,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7465,7 +7482,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7474,13 +7491,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7498,22 +7515,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>267</v>
+        <v>124</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7531,7 +7548,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7540,13 +7557,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7579,7 +7596,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7588,13 +7605,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7612,22 +7629,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7645,7 +7662,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7654,13 +7671,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7678,22 +7695,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7711,7 +7728,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7720,13 +7737,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7744,22 +7761,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7777,7 +7794,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7786,13 +7803,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7825,7 +7842,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7834,13 +7851,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7858,22 +7875,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>274</v>
+        <v>36</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7891,7 +7908,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7900,13 +7917,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7924,22 +7941,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7957,22 +7974,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8005,7 +8022,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8017,10 +8034,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8038,7 +8055,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8050,10 +8067,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8071,7 +8088,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8080,13 +8097,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>267</v>
+        <v>124</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8104,22 +8121,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8137,7 +8154,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8146,13 +8163,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8170,22 +8187,22 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8203,7 +8220,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8215,10 +8232,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8236,7 +8253,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8248,10 +8265,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8284,22 +8301,22 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8317,7 +8334,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8326,13 +8343,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8350,19 +8367,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>22</v>
@@ -8383,7 +8400,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8392,13 +8409,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8431,22 +8448,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8464,22 +8481,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8497,29 +8514,29 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="K229" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8549,7 +8566,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8558,13 +8575,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8582,22 +8599,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8615,7 +8632,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8627,7 +8644,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>22</v>
@@ -8648,7 +8665,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8660,10 +8677,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8696,22 +8713,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8729,22 +8746,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8762,22 +8779,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8810,7 +8827,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8819,13 +8836,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>296</v>
+        <v>123</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8843,22 +8860,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8876,7 +8893,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8885,13 +8902,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8909,22 +8926,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8942,7 +8959,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8951,13 +8968,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8975,29 +8992,29 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9027,7 +9044,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9036,13 +9053,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9060,22 +9077,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9093,22 +9110,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9126,22 +9143,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9159,7 +9176,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9168,20 +9185,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9211,7 +9228,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9220,13 +9237,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9244,22 +9261,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9277,7 +9294,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9286,13 +9303,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9310,22 +9327,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9343,7 +9360,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9352,13 +9369,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9376,22 +9393,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9409,7 +9426,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9421,10 +9438,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9442,7 +9459,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9454,7 +9471,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>26</v>
@@ -9490,7 +9507,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9499,13 +9516,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9523,22 +9540,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9556,7 +9573,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9565,13 +9582,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9589,22 +9606,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9633,26 +9650,26 @@
         <v>37</v>
       </c>
       <c t="s" r="C267" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9685,7 +9702,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9694,13 +9711,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>296</v>
+        <v>123</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9718,22 +9735,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9751,7 +9768,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9760,13 +9777,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9784,22 +9801,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9817,7 +9834,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9829,10 +9846,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9865,7 +9882,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9874,13 +9891,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9898,22 +9915,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9931,7 +9948,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9940,13 +9957,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9964,22 +9981,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9997,7 +10014,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10006,10 +10023,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>23</v>
@@ -10030,22 +10047,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10063,7 +10080,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10072,13 +10089,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10096,22 +10113,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10144,22 +10161,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10177,7 +10194,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10186,13 +10203,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10210,22 +10227,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10243,7 +10260,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10255,10 +10272,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10291,7 +10308,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10300,13 +10317,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10324,22 +10341,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10357,7 +10374,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10366,13 +10383,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10390,22 +10407,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10438,7 +10455,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10450,10 +10467,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10471,7 +10488,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10480,13 +10497,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10504,22 +10521,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10552,7 +10569,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10564,10 +10581,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10585,7 +10602,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10594,13 +10611,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10618,22 +10635,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10651,7 +10668,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10660,13 +10677,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10684,22 +10701,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10732,7 +10749,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10741,13 +10758,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
+        <v>108</v>
+      </c>
+      <c t="s" r="I304" s="7">
+        <v>290</v>
+      </c>
+      <c t="s" r="J304" s="7">
         <v>106</v>
-      </c>
-      <c t="s" r="I304" s="7">
-        <v>288</v>
-      </c>
-      <c t="s" r="J304" s="7">
-        <v>104</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10765,22 +10782,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10798,7 +10815,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10807,13 +10824,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10831,22 +10848,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10864,7 +10881,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10873,13 +10890,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10897,22 +10914,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10945,22 +10962,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10978,22 +10995,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11011,22 +11028,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11040,26 +11057,26 @@
         <v>5840</v>
       </c>
       <c t="s" r="C314" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11073,26 +11090,26 @@
         <v>5841</v>
       </c>
       <c t="s" r="C315" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11125,7 +11142,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11134,13 +11151,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11158,22 +11175,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11191,7 +11208,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11200,13 +11217,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11224,19 +11241,19 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>21</v>
@@ -11257,7 +11274,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11266,10 +11283,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>22</v>
@@ -11305,22 +11322,22 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11338,7 +11355,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11347,13 +11364,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11371,22 +11388,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11419,7 +11436,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11428,13 +11445,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11452,22 +11469,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11485,7 +11502,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11497,10 +11514,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11518,7 +11535,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11530,10 +11547,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11551,7 +11568,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11566,7 +11583,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11584,7 +11601,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11596,10 +11613,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11632,7 +11649,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11641,13 +11658,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11665,22 +11682,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11698,7 +11715,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11707,13 +11724,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11731,22 +11748,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11779,7 +11796,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11791,10 +11808,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11812,7 +11829,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11821,13 +11838,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11845,22 +11862,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11878,7 +11895,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11890,10 +11907,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11911,7 +11928,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11920,13 +11937,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11944,22 +11961,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11992,7 +12009,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12001,13 +12018,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12025,22 +12042,22 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12058,22 +12075,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12091,22 +12108,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12124,22 +12141,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12157,22 +12174,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12205,29 +12222,29 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>274</v>
+        <v>36</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12242,22 +12259,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12275,22 +12292,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12308,22 +12325,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12356,7 +12373,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12368,10 +12385,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12389,7 +12406,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12398,13 +12415,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12422,22 +12439,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12455,7 +12472,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12464,13 +12481,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12488,22 +12505,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12521,7 +12538,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12533,10 +12550,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12569,7 +12586,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12578,13 +12595,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12602,22 +12619,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12635,7 +12652,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12644,13 +12661,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12668,22 +12685,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12701,7 +12718,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12710,13 +12727,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12734,22 +12751,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12782,22 +12799,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12815,7 +12832,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12827,10 +12844,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12848,7 +12865,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12857,13 +12874,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12881,22 +12898,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12914,7 +12931,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12923,13 +12940,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12947,22 +12964,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12991,33 +13008,33 @@
         <v>5228</v>
       </c>
       <c t="s" r="C379" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13028,33 +13045,33 @@
         <v>5574</v>
       </c>
       <c t="s" r="C380" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F380" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="K380" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>296</v>
+        <v>123</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13084,7 +13101,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
@@ -13093,13 +13110,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13113,26 +13130,26 @@
         <v>6874</v>
       </c>
       <c t="s" r="C383" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F383" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13146,26 +13163,26 @@
         <v>6875</v>
       </c>
       <c t="s" r="C384" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13198,7 +13215,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13210,10 +13227,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13231,7 +13248,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
@@ -13243,10 +13260,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13264,7 +13281,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13276,10 +13293,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13297,7 +13314,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13306,13 +13323,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13345,7 +13362,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
@@ -13357,10 +13374,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13378,7 +13395,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
@@ -13390,10 +13407,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13411,7 +13428,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13423,10 +13440,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13459,7 +13476,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13468,13 +13485,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13492,22 +13509,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13525,22 +13542,22 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G397" s="8">
+        <v>380</v>
+      </c>
+      <c t="s" r="H397" s="8">
         <v>379</v>
       </c>
-      <c t="s" r="H397" s="8">
-        <v>378</v>
-      </c>
       <c t="s" r="I397" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13573,7 +13590,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13585,14 +13602,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>200</v>
-      </c>
-      <c r="K399" s="7"/>
+        <v>205</v>
+      </c>
+      <c t="s" r="K399" s="7">
+        <v>46</v>
+      </c>
       <c r="L399" s="7"/>
-      <c r="M399" s="7"/>
+      <c t="s" r="M399" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="400" ht="15" customHeight="1">
       <c t="s" r="A400" s="6">
@@ -13606,7 +13627,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13618,14 +13639,18 @@
         <v>20</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>18</v>
       </c>
-      <c r="K400" s="7"/>
+      <c t="s" r="K400" s="7">
+        <v>222</v>
+      </c>
       <c r="L400" s="7"/>
-      <c r="M400" s="7"/>
+      <c t="s" r="M400" s="7">
+        <v>38</v>
+      </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
       <c t="s" r="A401" s="6">
@@ -13639,7 +13664,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13648,13 +13673,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13672,22 +13697,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13705,7 +13730,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13717,10 +13742,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13753,7 +13778,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -13765,10 +13790,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13786,7 +13811,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -13798,10 +13823,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13834,7 +13859,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13843,13 +13868,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13867,22 +13892,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13890,7 +13915,7 @@
     </row>
     <row r="410" ht="16.5" customHeight="1">
       <c t="s" r="A410" s="9">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
@@ -13910,7 +13935,7 @@
     <row r="411" ht="65.25" customHeight="1"/>
     <row r="412" ht="16.5" customHeight="1">
       <c t="s" r="A412" s="10">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B412" s="10"/>
       <c r="C412" s="10"/>
@@ -13923,7 +13948,7 @@
       <c r="J412" s="10"/>
       <c r="K412" s="10"/>
       <c t="s" r="L412" s="11">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M412" s="11"/>
       <c r="N412" s="11"/>

--- a/Data/FlightPlan/FPL_27OCT26.xlsx
+++ b/Data/FlightPlan/FPL_27OCT26.xlsx
@@ -536,6 +536,15 @@
     <t>06:40</t>
   </si>
   <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
     <t>14:40</t>
   </si>
   <si>
@@ -545,7 +554,10 @@
     <t>17:20</t>
   </si>
   <si>
-    <t>19:30</t>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:55</t>
   </si>
   <si>
     <t>20:30</t>
@@ -554,384 +566,375 @@
     <t>23:10</t>
   </si>
   <si>
-    <t>VN-A549</t>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
   </si>
   <si>
     <t>07:00</t>
   </si>
   <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
     <t>09:10</t>
   </si>
   <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
     <t>11:35</t>
   </si>
   <si>
-    <t>UIH</t>
-  </si>
-  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -944,9 +947,6 @@
     <t>10:15</t>
   </si>
   <si>
-    <t>11:15</t>
-  </si>
-  <si>
     <t>HND</t>
   </si>
   <si>
@@ -1013,105 +1013,105 @@
     <t>VN-A668</t>
   </si>
   <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
     <t>22:55</t>
   </si>
   <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>03:25</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1172,7 +1172,7 @@
     <t>Total Record(s): 336</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 27, 2026 03:38</t>
+    <t xml:space="preserve">Generated on  Oct 27, 2026 04:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4650,7 +4650,7 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>129</v>
+        <v>523</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
@@ -4666,13 +4666,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>175</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4683,7 +4683,7 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>128</v>
+        <v>524</v>
       </c>
       <c t="s" r="C103" s="7">
         <v>14</v>
@@ -4696,16 +4696,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4716,7 +4716,7 @@
         <v>13</v>
       </c>
       <c r="B104" s="7">
-        <v>133</v>
+        <v>491</v>
       </c>
       <c t="s" r="C104" s="7">
         <v>14</v>
@@ -4732,13 +4732,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4749,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="B105" s="7">
-        <v>132</v>
+        <v>492</v>
       </c>
       <c t="s" r="C105" s="7">
         <v>14</v>
@@ -4762,16 +4762,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4797,14 +4797,14 @@
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>1139</v>
+        <v>129</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4816,28 +4816,32 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>183</v>
-      </c>
-      <c r="K107" s="7"/>
+        <v>179</v>
+      </c>
+      <c t="s" r="K107" s="7">
+        <v>92</v>
+      </c>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>55</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>1138</v>
+        <v>128</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4849,28 +4853,32 @@
         <v>20</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>185</v>
-      </c>
-      <c r="K108" s="7"/>
+        <v>176</v>
+      </c>
+      <c t="s" r="K108" s="7">
+        <v>181</v>
+      </c>
       <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
+      <c t="s" r="M108" s="7">
+        <v>182</v>
+      </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c t="s" r="A109" s="6">
         <v>13</v>
       </c>
       <c r="B109" s="7">
-        <v>523</v>
+        <v>133</v>
       </c>
       <c t="s" r="C109" s="7">
         <v>14</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4879,13 +4887,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4896,63 +4904,45 @@
         <v>13</v>
       </c>
       <c r="B110" s="7">
-        <v>524</v>
+        <v>132</v>
       </c>
       <c t="s" r="C110" s="7">
         <v>14</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c t="s" r="A111" s="6">
-        <v>13</v>
-      </c>
-      <c r="B111" s="7">
-        <v>491</v>
-      </c>
-      <c t="s" r="C111" s="7">
-        <v>14</v>
-      </c>
+      <c r="A111" s="6"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
       <c r="D111" s="7"/>
-      <c t="s" r="E111" s="7">
-        <v>181</v>
-      </c>
-      <c r="F111" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G111" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H111" s="8">
-        <v>105</v>
-      </c>
-      <c t="s" r="I111" s="7">
-        <v>137</v>
-      </c>
-      <c t="s" r="J111" s="7">
-        <v>168</v>
-      </c>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
@@ -4962,45 +4952,63 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>492</v>
+        <v>356</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H112" s="8">
         <v>105</v>
       </c>
-      <c t="s" r="H112" s="8">
-        <v>20</v>
-      </c>
       <c t="s" r="I112" s="7">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
+      <c t="s" r="A113" s="6">
+        <v>13</v>
+      </c>
+      <c r="B113" s="7">
+        <v>357</v>
+      </c>
+      <c t="s" r="C113" s="7">
+        <v>14</v>
+      </c>
       <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
+      <c t="s" r="E113" s="7">
+        <v>185</v>
+      </c>
+      <c r="F113" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G113" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="H113" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I113" s="7">
+        <v>27</v>
+      </c>
+      <c t="s" r="J113" s="7">
+        <v>187</v>
+      </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c r="M113" s="7"/>
@@ -5010,14 +5018,14 @@
         <v>13</v>
       </c>
       <c r="B114" s="7">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c t="s" r="C114" s="7">
         <v>14</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5026,13 +5034,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
+        <v>67</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5043,29 +5051,29 @@
         <v>13</v>
       </c>
       <c r="B115" s="7">
-        <v>357</v>
+        <v>320</v>
       </c>
       <c t="s" r="C115" s="7">
         <v>14</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5076,14 +5084,14 @@
         <v>13</v>
       </c>
       <c r="B116" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5095,10 +5103,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5109,14 +5117,14 @@
         <v>13</v>
       </c>
       <c r="B117" s="7">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c t="s" r="C117" s="7">
         <v>14</v>
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5128,10 +5136,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>61</v>
+        <v>191</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5142,14 +5150,14 @@
         <v>13</v>
       </c>
       <c r="B118" s="7">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c t="s" r="C118" s="7">
         <v>14</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5158,13 +5166,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5175,26 +5183,26 @@
         <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>193</v>
@@ -5208,14 +5216,14 @@
         <v>13</v>
       </c>
       <c r="B120" s="7">
-        <v>362</v>
+        <v>224</v>
       </c>
       <c t="s" r="C120" s="7">
         <v>14</v>
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5224,13 +5232,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>194</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5241,63 +5249,45 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>363</v>
+        <v>225</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c r="M121" s="7"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
-      <c t="s" r="A122" s="6">
-        <v>13</v>
-      </c>
-      <c r="B122" s="7">
-        <v>224</v>
-      </c>
-      <c t="s" r="C122" s="7">
-        <v>14</v>
-      </c>
+      <c r="A122" s="6"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
       <c r="D122" s="7"/>
-      <c t="s" r="E122" s="7">
-        <v>187</v>
-      </c>
-      <c r="F122" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G122" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H122" s="8">
-        <v>131</v>
-      </c>
-      <c t="s" r="I122" s="7">
-        <v>197</v>
-      </c>
-      <c t="s" r="J122" s="7">
-        <v>198</v>
-      </c>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c r="M122" s="7"/>
@@ -5307,78 +5297,78 @@
         <v>13</v>
       </c>
       <c r="B123" s="7">
-        <v>225</v>
+        <v>893</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>199</v>
+        <v>106</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="7"/>
+      <c t="s" r="A124" s="6">
+        <v>13</v>
+      </c>
+      <c r="B124" s="7">
+        <v>894</v>
+      </c>
+      <c t="s" r="C124" s="7">
+        <v>14</v>
+      </c>
       <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="8"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
+      <c t="s" r="E124" s="7">
+        <v>198</v>
+      </c>
+      <c r="F124" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G124" s="8">
+        <v>199</v>
+      </c>
+      <c t="s" r="H124" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I124" s="7">
+        <v>19</v>
+      </c>
+      <c t="s" r="J124" s="7">
+        <v>82</v>
+      </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c t="s" r="A125" s="6">
-        <v>13</v>
-      </c>
-      <c r="B125" s="7">
-        <v>893</v>
-      </c>
-      <c t="s" r="C125" s="7">
-        <v>14</v>
-      </c>
+      <c r="A125" s="6"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
       <c r="D125" s="7"/>
-      <c t="s" r="E125" s="7">
-        <v>201</v>
-      </c>
-      <c r="F125" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G125" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H125" s="8">
-        <v>202</v>
-      </c>
-      <c t="s" r="I125" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="J125" s="7">
-        <v>110</v>
-      </c>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="7"/>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
@@ -5388,10 +5378,10 @@
         <v>13</v>
       </c>
       <c r="B126" s="7">
-        <v>894</v>
+        <v>5521</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
@@ -5401,32 +5391,54 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H126" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I126" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J126" s="7">
         <v>202</v>
       </c>
-      <c t="s" r="H126" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I126" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="J126" s="7">
-        <v>82</v>
-      </c>
-      <c r="K126" s="7"/>
+      <c t="s" r="K126" s="7">
+        <v>46</v>
+      </c>
       <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
+      <c t="s" r="M126" s="7">
+        <v>103</v>
+      </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="7"/>
+      <c t="s" r="A127" s="6">
+        <v>13</v>
+      </c>
+      <c r="B127" s="7">
+        <v>328</v>
+      </c>
+      <c t="s" r="C127" s="7">
+        <v>14</v>
+      </c>
       <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
+      <c t="s" r="E127" s="7">
+        <v>201</v>
+      </c>
+      <c r="F127" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G127" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H127" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I127" s="7">
+        <v>203</v>
+      </c>
+      <c t="s" r="J127" s="7">
+        <v>204</v>
+      </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c r="M127" s="7"/>
@@ -5436,66 +5448,62 @@
         <v>13</v>
       </c>
       <c r="B128" s="7">
-        <v>5521</v>
+        <v>640</v>
       </c>
       <c t="s" r="C128" s="7">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>205</v>
-      </c>
-      <c t="s" r="K128" s="7">
-        <v>46</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-      <c t="s" r="M128" s="7">
-        <v>103</v>
-      </c>
+      <c r="M128" s="7"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
         <v>13</v>
       </c>
       <c r="B129" s="7">
-        <v>328</v>
+        <v>641</v>
       </c>
       <c t="s" r="C129" s="7">
         <v>14</v>
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5506,14 +5514,14 @@
         <v>13</v>
       </c>
       <c r="B130" s="7">
-        <v>640</v>
+        <v>244</v>
       </c>
       <c t="s" r="C130" s="7">
         <v>14</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5522,13 +5530,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5539,29 +5547,29 @@
         <v>13</v>
       </c>
       <c r="B131" s="7">
-        <v>641</v>
+        <v>251</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5572,14 +5580,14 @@
         <v>13</v>
       </c>
       <c r="B132" s="7">
-        <v>244</v>
+        <v>1140</v>
       </c>
       <c t="s" r="C132" s="7">
         <v>14</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5588,47 +5596,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c t="s" r="A133" s="6">
-        <v>13</v>
-      </c>
-      <c r="B133" s="7">
-        <v>251</v>
-      </c>
-      <c t="s" r="C133" s="7">
-        <v>14</v>
-      </c>
+      <c r="A133" s="6"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
       <c r="D133" s="7"/>
-      <c t="s" r="E133" s="7">
-        <v>204</v>
-      </c>
-      <c r="F133" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G133" s="8">
-        <v>208</v>
-      </c>
-      <c t="s" r="H133" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I133" s="7">
-        <v>179</v>
-      </c>
-      <c t="s" r="J133" s="7">
-        <v>162</v>
-      </c>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="7"/>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
@@ -5638,45 +5628,63 @@
         <v>13</v>
       </c>
       <c r="B134" s="7">
-        <v>1140</v>
+        <v>567</v>
       </c>
       <c t="s" r="C134" s="7">
         <v>14</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
+      <c t="s" r="A135" s="6">
+        <v>13</v>
+      </c>
+      <c r="B135" s="7">
+        <v>566</v>
+      </c>
+      <c t="s" r="C135" s="7">
+        <v>14</v>
+      </c>
       <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
+      <c t="s" r="E135" s="7">
+        <v>208</v>
+      </c>
+      <c r="F135" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G135" s="8">
+        <v>51</v>
+      </c>
+      <c t="s" r="H135" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="I135" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J135" s="7">
+        <v>187</v>
+      </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c r="M135" s="7"/>
@@ -5686,14 +5694,14 @@
         <v>13</v>
       </c>
       <c r="B136" s="7">
-        <v>567</v>
+        <v>447</v>
       </c>
       <c t="s" r="C136" s="7">
         <v>14</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5702,13 +5710,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5719,29 +5727,29 @@
         <v>13</v>
       </c>
       <c r="B137" s="7">
-        <v>566</v>
+        <v>448</v>
       </c>
       <c t="s" r="C137" s="7">
         <v>14</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>213</v>
+        <v>91</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5752,14 +5760,14 @@
         <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c t="s" r="C138" s="7">
         <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5768,13 +5776,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5785,29 +5793,29 @@
         <v>13</v>
       </c>
       <c r="B139" s="7">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c t="s" r="C139" s="7">
         <v>14</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>91</v>
+        <v>213</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5818,14 +5826,14 @@
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>465</v>
+        <v>1507</v>
       </c>
       <c t="s" r="C140" s="7">
         <v>14</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5834,13 +5842,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5851,26 +5859,26 @@
         <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>464</v>
+        <v>1508</v>
       </c>
       <c t="s" r="C141" s="7">
         <v>14</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>216</v>
@@ -5880,34 +5888,16 @@
       <c r="M141" s="7"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c t="s" r="A142" s="6">
-        <v>13</v>
-      </c>
-      <c r="B142" s="7">
-        <v>1507</v>
-      </c>
-      <c t="s" r="C142" s="7">
-        <v>14</v>
-      </c>
+      <c r="A142" s="6"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
       <c r="D142" s="7"/>
-      <c t="s" r="E142" s="7">
-        <v>211</v>
-      </c>
-      <c r="F142" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G142" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H142" s="8">
-        <v>108</v>
-      </c>
-      <c t="s" r="I142" s="7">
-        <v>199</v>
-      </c>
-      <c t="s" r="J142" s="7">
-        <v>217</v>
-      </c>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
@@ -5917,45 +5907,63 @@
         <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>1508</v>
+        <v>396</v>
       </c>
       <c t="s" r="C143" s="7">
         <v>14</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="7"/>
+      <c t="s" r="A144" s="6">
+        <v>13</v>
+      </c>
+      <c r="B144" s="7">
+        <v>397</v>
+      </c>
+      <c t="s" r="C144" s="7">
+        <v>14</v>
+      </c>
       <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
+      <c t="s" r="E144" s="7">
+        <v>217</v>
+      </c>
+      <c r="F144" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G144" s="8">
+        <v>218</v>
+      </c>
+      <c t="s" r="H144" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I144" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J144" s="7">
+        <v>220</v>
+      </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c r="M144" s="7"/>
@@ -5965,14 +5973,14 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>396</v>
+        <v>638</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5981,13 +5989,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5998,29 +6006,29 @@
         <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>397</v>
+        <v>639</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>106</v>
+        <v>221</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6031,14 +6039,14 @@
         <v>13</v>
       </c>
       <c r="B147" s="7">
-        <v>638</v>
+        <v>226</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6047,13 +6055,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6064,29 +6072,29 @@
         <v>13</v>
       </c>
       <c r="B148" s="7">
-        <v>639</v>
+        <v>227</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>223</v>
+        <v>144</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6097,14 +6105,14 @@
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c t="s" r="C149" s="7">
         <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6113,47 +6121,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>224</v>
+        <v>139</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c t="s" r="A150" s="6">
-        <v>13</v>
-      </c>
-      <c r="B150" s="7">
-        <v>227</v>
-      </c>
-      <c t="s" r="C150" s="7">
-        <v>14</v>
-      </c>
+      <c r="A150" s="6"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
       <c r="D150" s="7"/>
-      <c t="s" r="E150" s="7">
-        <v>219</v>
-      </c>
-      <c r="F150" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G150" s="8">
-        <v>131</v>
-      </c>
-      <c t="s" r="H150" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I150" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J150" s="7">
-        <v>226</v>
-      </c>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="7"/>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
@@ -6163,14 +6153,14 @@
         <v>13</v>
       </c>
       <c r="B151" s="7">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c t="s" r="C151" s="7">
         <v>14</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6179,29 +6169,47 @@
         <v>17</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="7"/>
+      <c t="s" r="A152" s="6">
+        <v>13</v>
+      </c>
+      <c r="B152" s="7">
+        <v>383</v>
+      </c>
+      <c t="s" r="C152" s="7">
+        <v>14</v>
+      </c>
       <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="8"/>
-      <c r="H152" s="8"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
+      <c t="s" r="E152" s="7">
+        <v>225</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="H152" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I152" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="J152" s="7">
+        <v>98</v>
+      </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
@@ -6218,7 +6226,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6247,11 +6255,11 @@
         <v>6888</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6266,7 +6274,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6280,11 +6288,11 @@
         <v>6888</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6293,10 +6301,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>127</v>
@@ -6332,7 +6340,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6344,10 +6352,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="K157" s="7">
         <v>127</v>
@@ -6369,7 +6377,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6417,7 +6425,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6426,13 +6434,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6450,19 +6458,19 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>135</v>
@@ -6483,7 +6491,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6495,10 +6503,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6516,7 +6524,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6549,7 +6557,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6558,13 +6566,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6582,22 +6590,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6630,7 +6638,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6642,10 +6650,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6663,7 +6671,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6678,7 +6686,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6696,7 +6704,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6711,7 +6719,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6729,7 +6737,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6744,7 +6752,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6762,7 +6770,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6795,7 +6803,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6807,10 +6815,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6843,7 +6851,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6855,7 +6863,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>52</v>
@@ -6876,7 +6884,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6885,13 +6893,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6909,22 +6917,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6942,7 +6950,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6975,7 +6983,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7023,7 +7031,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7035,7 +7043,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>80</v>
@@ -7056,7 +7064,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7089,7 +7097,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7098,13 +7106,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="I182" s="7">
         <v>167</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7122,19 +7130,19 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>162</v>
@@ -7155,7 +7163,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7164,13 +7172,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7188,22 +7196,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7236,7 +7244,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7248,10 +7256,10 @@
         <v>131</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7269,7 +7277,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7284,7 +7292,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7302,7 +7310,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7317,7 +7325,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7335,7 +7343,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7347,10 +7355,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7368,7 +7376,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7377,13 +7385,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7401,22 +7409,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7449,7 +7457,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7464,7 +7472,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7482,7 +7490,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7497,7 +7505,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7515,7 +7523,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7548,7 +7556,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7596,7 +7604,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7608,7 +7616,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>149</v>
@@ -7629,7 +7637,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7641,7 +7649,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>107</v>
@@ -7662,7 +7670,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7674,10 +7682,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7695,7 +7703,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7707,7 +7715,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>125</v>
@@ -7728,7 +7736,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7737,13 +7745,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7761,13 +7769,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>17</v>
@@ -7794,7 +7802,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7806,7 +7814,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>160</v>
@@ -7842,7 +7850,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7854,7 +7862,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>106</v>
@@ -7875,7 +7883,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7908,7 +7916,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7920,10 +7928,10 @@
         <v>166</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7941,7 +7949,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7950,13 +7958,13 @@
         <v>166</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7974,22 +7982,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>166</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8022,7 +8030,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8034,10 +8042,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8055,7 +8063,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8067,7 +8075,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>132</v>
@@ -8088,7 +8096,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8097,10 +8105,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>124</v>
@@ -8121,22 +8129,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8154,7 +8162,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8187,7 +8195,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8202,7 +8210,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8220,7 +8228,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8232,7 +8240,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>117</v>
@@ -8253,7 +8261,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8265,10 +8273,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8301,7 +8309,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8313,10 +8321,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8334,7 +8342,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8343,10 +8351,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>40</v>
@@ -8367,13 +8375,13 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>20</v>
@@ -8400,7 +8408,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8415,7 +8423,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8448,7 +8456,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8457,13 +8465,13 @@
         <v>108</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8481,22 +8489,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>108</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8514,7 +8522,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8529,14 +8537,14 @@
         <v>153</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>153</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -8566,7 +8574,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8578,10 +8586,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8599,7 +8607,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8632,7 +8640,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8665,7 +8673,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8680,7 +8688,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8713,7 +8721,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8722,10 +8730,10 @@
         <v>108</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>68</v>
@@ -8746,13 +8754,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>108</v>
@@ -8761,7 +8769,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8779,7 +8787,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8791,7 +8799,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>149</v>
@@ -8827,7 +8835,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8839,7 +8847,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>123</v>
@@ -8860,7 +8868,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8872,7 +8880,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>67</v>
@@ -8893,7 +8901,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8926,7 +8934,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8959,7 +8967,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8971,10 +8979,10 @@
         <v>108</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8992,7 +9000,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9004,7 +9012,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>153</v>
@@ -9014,7 +9022,7 @@
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9044,7 +9052,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9056,10 +9064,10 @@
         <v>166</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9077,7 +9085,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9089,10 +9097,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9110,7 +9118,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9122,7 +9130,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>114</v>
@@ -9143,7 +9151,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9158,7 +9166,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9176,7 +9184,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9194,11 +9202,11 @@
         <v>139</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9228,7 +9236,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9237,13 +9245,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9261,13 +9269,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
@@ -9276,7 +9284,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>183</v>
+        <v>306</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9294,7 +9302,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9309,7 +9317,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9327,7 +9335,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9360,7 +9368,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9369,10 +9377,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>158</v>
@@ -9393,13 +9401,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>17</v>
@@ -9426,7 +9434,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9459,7 +9467,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -9471,7 +9479,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>26</v>
@@ -9507,7 +9515,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9516,13 +9524,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>149</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9540,19 +9548,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>311</v>
+        <v>227</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>91</v>
@@ -9573,7 +9581,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9585,7 +9593,7 @@
         <v>312</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>313</v>
@@ -9606,7 +9614,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9621,7 +9629,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9666,7 +9674,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>318</v>
@@ -9711,10 +9719,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>123</v>
@@ -9741,16 +9749,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9777,13 +9785,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9807,7 +9815,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>17</v>
@@ -9816,7 +9824,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9891,10 +9899,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>142</v>
@@ -9921,7 +9929,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>20</v>
@@ -9930,7 +9938,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10023,10 +10031,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>23</v>
@@ -10053,7 +10061,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>20</v>
@@ -10089,7 +10097,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>73</v>
@@ -10119,7 +10127,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>20</v>
@@ -10173,7 +10181,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>91</v>
@@ -10203,13 +10211,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10233,7 +10241,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>20</v>
@@ -10275,7 +10283,7 @@
         <v>328</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10320,7 +10328,7 @@
         <v>330</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>109</v>
@@ -10353,10 +10361,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10386,10 +10394,10 @@
         <v>173</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10419,7 +10427,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>318</v>
@@ -10467,7 +10475,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>35</v>
@@ -10497,7 +10505,7 @@
         <v>20</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>332</v>
@@ -10527,7 +10535,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>20</v>
@@ -10562,7 +10570,7 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>151</v>
+        <v>1139</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
@@ -10581,10 +10589,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>127</v>
+        <v>272</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10595,7 +10603,7 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>807</v>
+        <v>1138</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
@@ -10611,13 +10619,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>321</v>
+        <v>203</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10628,7 +10636,7 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
@@ -10641,27 +10649,31 @@
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>167</v>
-      </c>
-      <c r="K300" s="7"/>
+        <v>265</v>
+      </c>
+      <c t="s" r="K300" s="7">
+        <v>91</v>
+      </c>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>111</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>314</v>
+        <v>5018</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
@@ -10677,13 +10689,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10694,7 +10706,7 @@
         <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>313</v>
+        <v>5019</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
@@ -10707,16 +10719,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10749,7 +10761,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10761,7 +10773,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>106</v>
@@ -10782,7 +10794,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10797,7 +10809,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10815,7 +10827,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10827,7 +10839,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>165</v>
@@ -10848,7 +10860,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10860,7 +10872,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>81</v>
@@ -10881,7 +10893,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10890,13 +10902,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10914,13 +10926,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>17</v>
@@ -10929,7 +10941,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10962,7 +10974,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10977,7 +10989,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10995,7 +11007,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11010,7 +11022,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11028,7 +11040,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11057,11 +11069,11 @@
         <v>5840</v>
       </c>
       <c t="s" r="C314" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11070,13 +11082,13 @@
         <v>108</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11090,26 +11102,26 @@
         <v>5841</v>
       </c>
       <c t="s" r="C315" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>108</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11142,7 +11154,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11154,10 +11166,10 @@
         <v>69</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11175,7 +11187,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11187,10 +11199,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11208,7 +11220,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11217,7 +11229,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>125</v>
@@ -11241,19 +11253,19 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>21</v>
@@ -11274,7 +11286,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11286,7 +11298,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>22</v>
@@ -11322,7 +11334,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11337,7 +11349,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11355,7 +11367,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11364,13 +11376,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11388,22 +11400,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11436,7 +11448,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11445,13 +11457,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11469,13 +11481,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>20</v>
@@ -11484,7 +11496,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11502,7 +11514,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11535,7 +11547,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11568,7 +11580,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11583,7 +11595,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11601,7 +11613,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11613,10 +11625,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11649,7 +11661,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11661,7 +11673,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>109</v>
@@ -11682,7 +11694,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11694,10 +11706,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11715,7 +11727,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11724,13 +11736,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11748,22 +11760,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11796,7 +11808,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11811,7 +11823,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11829,7 +11841,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11838,7 +11850,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>78</v>
@@ -11862,19 +11874,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>322</v>
@@ -11895,7 +11907,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -11907,10 +11919,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11928,7 +11940,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11943,7 +11955,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11961,7 +11973,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12009,7 +12021,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12021,10 +12033,10 @@
         <v>99</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12042,7 +12054,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12075,7 +12087,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12108,7 +12120,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12141,7 +12153,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12174,7 +12186,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12222,7 +12234,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12240,11 +12252,11 @@
         <v>36</v>
       </c>
       <c t="s" r="K353" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12259,7 +12271,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12268,10 +12280,10 @@
         <v>166</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>40</v>
@@ -12292,13 +12304,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>166</v>
@@ -12325,7 +12337,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12337,7 +12349,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>96</v>
@@ -12373,7 +12385,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12388,7 +12400,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12406,7 +12418,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12415,13 +12427,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12439,13 +12451,13 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>20</v>
@@ -12472,7 +12484,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12487,7 +12499,7 @@
         <v>322</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12505,7 +12517,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12517,7 +12529,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>101</v>
@@ -12538,7 +12550,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12550,7 +12562,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>102</v>
@@ -12586,7 +12598,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12595,10 +12607,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>33</v>
@@ -12619,19 +12631,19 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>332</v>
@@ -12645,14 +12657,14 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>382</v>
+        <v>807</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12661,13 +12673,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>306</v>
+        <v>69</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12678,29 +12690,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>383</v>
+        <v>800</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>306</v>
+        <v>69</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12711,14 +12723,14 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>5018</v>
+        <v>314</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12727,13 +12739,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>364</v>
+        <v>51</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>365</v>
+        <v>267</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12744,26 +12756,26 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>5019</v>
+        <v>313</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>364</v>
+        <v>51</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>366</v>
@@ -12811,10 +12823,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12825,7 +12837,7 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
@@ -12844,10 +12856,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>283</v>
+        <v>127</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12880,7 +12892,7 @@
         <v>369</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12913,7 +12925,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12940,10 +12952,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>73</v>
@@ -12970,7 +12982,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
@@ -13008,7 +13020,7 @@
         <v>5228</v>
       </c>
       <c t="s" r="C379" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
@@ -13024,13 +13036,13 @@
         <v>371</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>322</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
@@ -13045,7 +13057,7 @@
         <v>5574</v>
       </c>
       <c t="s" r="C380" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
@@ -13064,7 +13076,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="K380" s="7">
         <v>372</v>
@@ -13130,7 +13142,7 @@
         <v>6874</v>
       </c>
       <c t="s" r="C383" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
@@ -13163,7 +13175,7 @@
         <v>6875</v>
       </c>
       <c t="s" r="C384" s="7">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
@@ -13227,10 +13239,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13374,10 +13386,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13491,7 +13503,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>311</v>
+        <v>227</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13521,7 +13533,7 @@
         <v>380</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>113</v>
@@ -13602,10 +13614,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c t="s" r="K399" s="7">
         <v>46</v>
@@ -13645,7 +13657,7 @@
         <v>18</v>
       </c>
       <c t="s" r="K400" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
@@ -13790,7 +13802,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>67</v>
@@ -13871,7 +13883,7 @@
         <v>385</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>74</v>
@@ -13904,10 +13916,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
